--- a/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="MonsterProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -35,6 +35,25 @@
   </si>
   <si>
     <t>GroupId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster4400001</t>
+  </si>
+  <si>
+    <t>Monster4400002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -407,16 +426,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:E7"/>
+  <dimension ref="C3:F7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -426,8 +446,11 @@
       <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="F3" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -437,8 +460,11 @@
       <c r="E4" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="F4" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -448,8 +474,11 @@
       <c r="E5" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="F5" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>4400001</v>
       </c>
@@ -459,8 +488,11 @@
       <c r="E6" s="1">
         <v>3001</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>4400002</v>
       </c>
@@ -469,6 +501,9 @@
       </c>
       <c r="E7" s="1">
         <v>3002</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -46,14 +46,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Monster4400001</t>
-  </si>
-  <si>
-    <t>Monster4400002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>模型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster44001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster44002</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -447,7 +448,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="3:6" x14ac:dyDescent="0.3">
@@ -480,7 +481,7 @@
     </row>
     <row r="6" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
-        <v>4400001</v>
+        <v>44001</v>
       </c>
       <c r="D6" s="1">
         <v>10001</v>
@@ -489,12 +490,12 @@
         <v>3001</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
-        <v>4400002</v>
+        <v>44002</v>
       </c>
       <c r="D7" s="1">
         <v>10002</v>
@@ -503,7 +504,7 @@
         <v>3002</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A892624-64DA-4017-92FF-20BDB08F8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13065"/>
+    <workbookView xWindow="2400" yWindow="2775" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterProto" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="41">
   <si>
     <t>Id</t>
   </si>
@@ -55,13 +61,133 @@
   </si>
   <si>
     <t>Monster44002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理防御</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Def</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小魔法攻击</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理攻击</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7,10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAtk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDef</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>95%miss</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flee</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻速</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>移速</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击距离（普攻）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -119,13 +245,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -136,14 +265,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,7 +313,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -253,7 +385,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -426,18 +558,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C3:R7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="5" width="12.625" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="7" max="9" width="14.125" style="2" customWidth="1"/>
+    <col min="10" max="18" width="12.625" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -450,8 +584,44 @@
       <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="G3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -464,8 +634,44 @@
       <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -478,8 +684,44 @@
       <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="G5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>44001</v>
       </c>
@@ -492,8 +734,44 @@
       <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>50</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="1">
+        <v>202</v>
+      </c>
+      <c r="O6" s="1">
+        <v>177</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>2000</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:18" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>44002</v>
       </c>
@@ -505,6 +783,42 @@
       </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>50</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="1">
+        <v>202</v>
+      </c>
+      <c r="O7" s="1">
+        <v>177</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>2000</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
